--- a/Excel/JiaYuanFarmConfig.xlsx
+++ b/Excel/JiaYuanFarmConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64C6E0E-7F49-4C1D-B0B5-1C97274718DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769FCF1D-B299-4518-9458-290B4B5A8AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{874F2130-3ADA-411C-A78F-71CE4E6A1D1E}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{874F2130-3ADA-411C-A78F-71CE4E6A1D1E}">
       <text>
         <r>
           <rPr>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="107">
   <si>
     <t>Id</t>
   </si>
@@ -417,6 +417,67 @@
   </si>
   <si>
     <t>12240,30600,73440,146880</t>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zzzzz...</t>
+  </si>
+  <si>
+    <t>When mature, can obtain: Onion</t>
+  </si>
+  <si>
+    <t>When mature, you can obtain: Garlic</t>
+  </si>
+  <si>
+    <t>When matured, obtain: Carrot</t>
+  </si>
+  <si>
+    <t>When mature, you can obtain: carrot</t>
+  </si>
+  <si>
+    <t>When mature, you can obtain: Sweet Potato</t>
+  </si>
+  <si>
+    <t>When matured, it can provide: Cabbage</t>
+  </si>
+  <si>
+    <t>When mature, you can obtain: potatoes</t>
+  </si>
+  <si>
+    <t>Upon reaching maturity, you can obtain: Watermelon</t>
+  </si>
+  <si>
+    <t>When mature, can obtain: Pumpkin</t>
+  </si>
+  <si>
+    <t>When mature, you can obtain: Cucumber</t>
+  </si>
+  <si>
+    <t>When mature, you can obtain: tomatoes</t>
+  </si>
+  <si>
+    <t>When mature, can obtain: Wheat</t>
+  </si>
+  <si>
+    <t>What can be obtained when mature: Corn</t>
+  </si>
+  <si>
+    <t>When mature, you can obtain: Sunflower</t>
+  </si>
+  <si>
+    <t>Speak_EN</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Des_EN</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1634,7 +1695,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1661,6 +1722,7 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="315">
     <cellStyle name="20% - 强调文字颜色 1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2305,26 +2367,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:O23"/>
+  <dimension ref="C1:R23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="6" width="17.875" customWidth="1"/>
-    <col min="7" max="7" width="37" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="12" width="16.75" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="16.75" customWidth="1"/>
+    <col min="4" max="7" width="17.875" customWidth="1"/>
+    <col min="8" max="8" width="37" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="14" width="16.75" customWidth="1"/>
+    <col min="15" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:15" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="G1"/>
-      <c r="I1"/>
+    <row r="1" spans="3:18" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="H1"/>
       <c r="J1"/>
       <c r="K1"/>
-      <c r="O1"/>
+      <c r="L1"/>
+      <c r="R1"/>
     </row>
-    <row r="3" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="E2" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2332,40 +2405,49 @@
         <v>59</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="N3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2373,40 +2455,49 @@
         <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="P4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
@@ -2414,16 +2505,16 @@
         <v>73</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>10</v>
@@ -2435,609 +2526,716 @@
         <v>10</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>73</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="R5" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C6" s="4">
         <v>100101</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="4">
+      <c r="G6" s="4">
         <v>100101</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <v>1</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>1000</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="8">
+      <c r="L6" s="8">
         <v>10033001</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="N6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="9">
+      <c r="P6" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q6" s="9">
         <v>6479.9999999999991</v>
       </c>
-      <c r="O6" s="9">
+      <c r="R6" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="4">
         <v>100201</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G7" s="4">
         <v>100201</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="5">
+      <c r="I7" s="5">
         <v>1</v>
       </c>
-      <c r="I7" s="5">
-        <f t="shared" ref="I7:I11" si="0">I6+200</f>
+      <c r="J7" s="5">
+        <f t="shared" ref="J7:J11" si="0">J6+200</f>
         <v>1200</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="K7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="8">
+      <c r="L7" s="8">
         <v>10033002</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="M7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="N7" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="9">
+      <c r="P7" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q7" s="9">
         <v>7559.9999999999991</v>
       </c>
-      <c r="O7" s="9">
+      <c r="R7" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="4">
         <v>100301</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G8" s="4">
         <v>100301</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="5">
+      <c r="I8" s="5">
         <v>1</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="5">
         <f t="shared" si="0"/>
         <v>1400</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="K8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="8">
+      <c r="L8" s="8">
         <v>10033003</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="M8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="N8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="N8" s="9">
+      <c r="P8" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8" s="9">
         <v>8640.0000000000018</v>
       </c>
-      <c r="O8" s="9">
+      <c r="R8" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="4">
         <v>100401</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" s="4">
         <v>100401</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="5">
+      <c r="I9" s="5">
         <v>1</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="5">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="K9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="8">
+      <c r="L9" s="8">
         <v>10033004</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="M9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="N9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="N9" s="9">
+      <c r="P9" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q9" s="9">
         <v>9720</v>
       </c>
-      <c r="O9" s="9">
+      <c r="R9" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="4">
         <v>100501</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="4"/>
+      <c r="F10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="4">
+      <c r="G10" s="4">
         <v>100501</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="5">
+      <c r="I10" s="5">
         <v>1</v>
       </c>
-      <c r="I10" s="5">
+      <c r="J10" s="5">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="K10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="8">
+      <c r="L10" s="8">
         <v>10033005</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="M10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="N10" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O10" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="9">
+      <c r="P10" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q10" s="9">
         <v>10800</v>
       </c>
-      <c r="O10" s="9">
+      <c r="R10" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C11" s="4">
         <v>100601</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="4">
         <v>100601</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="5">
+      <c r="I11" s="5">
         <v>1</v>
       </c>
-      <c r="I11" s="5">
+      <c r="J11" s="5">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="8">
+      <c r="L11" s="8">
         <v>10033006</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="M11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="N11" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="9">
+      <c r="P11" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q11" s="9">
         <v>11880.000000000002</v>
       </c>
-      <c r="O11" s="9">
+      <c r="R11" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C12" s="4">
         <v>100701</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="4">
+      <c r="G12" s="4">
         <v>100701</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="5">
+      <c r="I12" s="5">
         <v>1</v>
       </c>
-      <c r="I12" s="5">
-        <f>I11+300</f>
+      <c r="J12" s="5">
+        <f>J11+300</f>
         <v>2300</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K12" s="8">
+      <c r="L12" s="8">
         <v>10033007</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="M12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="N12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="9">
+      <c r="P12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q12" s="9">
         <v>12959.999999999998</v>
       </c>
-      <c r="O12" s="9">
+      <c r="R12" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C13" s="4">
         <v>100801</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="4">
+      <c r="G13" s="4">
         <v>100801</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="H13" s="5">
+      <c r="I13" s="5">
         <v>1</v>
       </c>
-      <c r="I13" s="5">
-        <f>I12+300</f>
+      <c r="J13" s="5">
+        <f>J12+300</f>
         <v>2600</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="K13" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="8">
+      <c r="L13" s="8">
         <v>10033008</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="M13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="N13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="N13" s="9">
+      <c r="P13" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q13" s="9">
         <v>14040.000000000002</v>
       </c>
-      <c r="O13" s="9">
+      <c r="R13" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="4">
         <v>100901</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="4"/>
+      <c r="F14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="5">
+      <c r="I14" s="5">
         <v>1</v>
       </c>
-      <c r="I14" s="5">
-        <f t="shared" ref="I14:I19" si="1">I13+400</f>
+      <c r="J14" s="5">
+        <f t="shared" ref="J14:J19" si="1">J13+400</f>
         <v>3000</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="K14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="8">
+      <c r="L14" s="8">
         <v>10033009</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="M14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="N14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="N14" s="9">
+      <c r="P14" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" s="9">
         <v>15119.999999999998</v>
       </c>
-      <c r="O14" s="9">
+      <c r="R14" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="4">
         <v>101001</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="4">
+      <c r="G15" s="4">
         <v>101001</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="5">
+      <c r="I15" s="5">
         <v>1</v>
       </c>
-      <c r="I15" s="5">
+      <c r="J15" s="5">
         <f t="shared" si="1"/>
         <v>3400</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="K15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="8">
+      <c r="L15" s="8">
         <v>10033010</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="M15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="N15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="N15" s="9">
+      <c r="P15" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="9">
         <v>16200</v>
       </c>
-      <c r="O15" s="9">
+      <c r="R15" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="4">
         <v>101101</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="4"/>
+      <c r="F16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="4">
+      <c r="G16" s="4">
         <v>101101</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="5">
+      <c r="I16" s="5">
         <v>1</v>
       </c>
-      <c r="I16" s="5">
+      <c r="J16" s="5">
         <f t="shared" si="1"/>
         <v>3800</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="K16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="8">
+      <c r="L16" s="8">
         <v>10033011</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="M16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="N16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O16" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="N16" s="9">
+      <c r="P16" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q16" s="9">
         <v>17280.000000000004</v>
       </c>
-      <c r="O16" s="9">
+      <c r="R16" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="4">
         <v>101201</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="4"/>
+      <c r="F17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="4">
+      <c r="G17" s="4">
         <v>101201</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="5">
+      <c r="I17" s="5">
         <v>1</v>
       </c>
-      <c r="I17" s="5">
+      <c r="J17" s="5">
         <f t="shared" si="1"/>
         <v>4200</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="K17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K17" s="8">
+      <c r="L17" s="8">
         <v>10033012</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="M17" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M17" s="5" t="s">
+      <c r="N17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="N17" s="9">
+      <c r="P17" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q17" s="9">
         <v>18360</v>
       </c>
-      <c r="O17" s="9">
+      <c r="R17" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="4">
         <v>101301</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="4">
         <v>101301</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="5">
+      <c r="I18" s="5">
         <v>1</v>
       </c>
-      <c r="I18" s="5">
+      <c r="J18" s="5">
         <f t="shared" si="1"/>
         <v>4600</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="K18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="8">
+      <c r="L18" s="8">
         <v>10033013</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="M18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M18" s="5" t="s">
+      <c r="N18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="9">
+      <c r="P18" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q18" s="9">
         <v>19440</v>
       </c>
-      <c r="O18" s="9">
+      <c r="R18" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="4">
         <v>101401</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="4"/>
+      <c r="F19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="4">
+      <c r="G19" s="4">
         <v>101401</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H19" s="5">
+      <c r="I19" s="5">
         <v>1</v>
       </c>
-      <c r="I19" s="5">
+      <c r="J19" s="5">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="K19" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="8">
+      <c r="L19" s="8">
         <v>10033014</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="M19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="N19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="N19" s="9">
+      <c r="P19" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q19" s="9">
         <v>21600</v>
       </c>
-      <c r="O19" s="9">
+      <c r="R19" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="3:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="3:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/JiaYuanFarmConfig.xlsx
+++ b/Excel/JiaYuanFarmConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769FCF1D-B299-4518-9458-290B4B5A8AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FFA170-72B8-4B43-A622-0CFC97D8D783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JiaYuanFarmProto" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="121">
   <si>
     <t>Id</t>
   </si>
@@ -478,6 +478,55 @@
   <si>
     <t>Des_EN</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scallion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Garlic</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Watermelon</t>
+  </si>
+  <si>
+    <t>Cucumber</t>
+  </si>
+  <si>
+    <t>Sunflower</t>
+  </si>
+  <si>
+    <t>Carrot</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Red Radish</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sweet Potato</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cabbage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Potato</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Squash</t>
+  </si>
+  <si>
+    <t>Tomato</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Corn </t>
   </si>
 </sst>
 </file>
@@ -2554,7 +2603,9 @@
       <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>107</v>
+      </c>
       <c r="F6" s="4" t="s">
         <v>3</v>
       </c>
@@ -2602,7 +2653,9 @@
       <c r="D7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>108</v>
+      </c>
       <c r="F7" s="4" t="s">
         <v>4</v>
       </c>
@@ -2651,7 +2704,9 @@
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="F8" s="4" t="s">
         <v>14</v>
       </c>
@@ -2700,7 +2755,9 @@
       <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="F9" s="4" t="s">
         <v>16</v>
       </c>
@@ -2749,7 +2806,9 @@
       <c r="D10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="F10" s="4" t="s">
         <v>18</v>
       </c>
@@ -2798,7 +2857,9 @@
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="F11" s="4" t="s">
         <v>20</v>
       </c>
@@ -2847,7 +2908,9 @@
       <c r="D12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="F12" s="4" t="s">
         <v>22</v>
       </c>
@@ -2896,7 +2959,9 @@
       <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="F13" s="4" t="s">
         <v>24</v>
       </c>
@@ -2945,7 +3010,9 @@
       <c r="D14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="F14" s="4" t="s">
         <v>26</v>
       </c>
@@ -2994,7 +3061,9 @@
       <c r="D15" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>110</v>
+      </c>
       <c r="F15" s="4" t="s">
         <v>28</v>
       </c>
@@ -3043,7 +3112,9 @@
       <c r="D16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="F16" s="4" t="s">
         <v>30</v>
       </c>
@@ -3092,7 +3163,9 @@
       <c r="D17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="F17" s="4" t="s">
         <v>32</v>
       </c>
@@ -3141,7 +3214,9 @@
       <c r="D18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="F18" s="4" t="s">
         <v>34</v>
       </c>
@@ -3190,7 +3265,9 @@
       <c r="D19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="F19" s="4" t="s">
         <v>36</v>
       </c>
